--- a/TESTS/zlit_5_poeziia_kits_hete.xlsx
+++ b/TESTS/zlit_5_poeziia_kits_hete.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Джон Кітс — видатний англійський поет-романтик</t>
+          <t>Джон Кітс</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Романтизм — Кітс один з найяскравіших представників англійського романтизму</t>
+          <t>Романтизм</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Англія — Кітс народився у Лондоні у 1795 році</t>
+          <t>Англія</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Природа ніколи не замовкає — літом співає коник взимку цвіркун і так природа звучить вічно</t>
+          <t>Природа ніколи не замовкає</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Коник і цвіркун — вони символізують безперервний голос природи влітку і взимку</t>
+          <t>Коник і цвіркун</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Літо і зима — але обидві пори сповнені звуками природи коник влітку цвіркун взимку</t>
+          <t>Літо і зима</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Сонет — чотирнадцятирядковий вірш з певним римуванням</t>
+          <t>Сонет</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Голос землі влітку — невтомна радість природи яка не замовкає навіть у спеку</t>
+          <t>Голос землі влітку</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Голос природи взимку — тепло домашнього вогнища і продовження природної пісні у холодну пору</t>
+          <t>Голос природи взимку</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Скільки років прожив Джон Кітс?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Понад 70 років</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дуже мало — він помер молодим, у 25 років, від хвороби</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Близько 50 років</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Понад 90 років</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Чим прославився Джон Кітс попри коротке життя?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Романами</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Витонченою романтичною поезією про красу природи й почуття</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Драматургією</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Науковими працями</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Коли, за віршем «Про коника та цвіркуна», звучить «голос землі»?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише вночі</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Завжди — влітку його несе коник, а взимку — цвіркун</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лише вранці</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише навесні</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Що робить коник (кобилка) у вірші Кітса влітку?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Мовчить</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Літає від куща до куща і не перестає співати в спекотний день</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Спить у траві</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Тікає від спеки</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Яку пору доби/року найбільше пов'язано з піснею коника у вірші?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Зимову ніч</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Спекотний літній день</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Осінній вечір</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Весняний ранок</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Чому образ коника асоціюється саме з повнотою життя влітку?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо коник найбільша комаха</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо його невпинна пісня звучить серед розкішної літньої природи</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо коник співає лише раз на рік</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо коник зелений</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Де, за віршем Кітса, чути пісню цвіркуна взимку?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У лісі</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Біля теплої печі, в домашньому затишку</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>На вулиці</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>У полі</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Яке враження створює пісня цвіркуна в зимовій тиші, за віршем?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лякає</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Створює відчуття тепла, домашнього затишку й тихої радості серед зимового спокою</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Створює сум</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Створює тривогу</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Як співвідносяться між собою пісні коника і цвіркуна за змістом вірша?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони ніяк не пов'язані</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони ніби продовжують одна одну, утворюючи безперервний «голос землі» цілий рік</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Цвіркун співає краще</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Коник співає лише вночі</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>До якої країни і епохи належить Йоганн Вольфганг Гете?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Франція, Просвітництво</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Німеччина, межа XVIII-XIX століть</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Італія, Ренесанс</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Англія, Вікторіанська епоха</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Чим, крім поезії, займався Гете протягом життя?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише поезією</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Був ученим, державним діячем — людиною різноманітних талантів</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лише музикою</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише живописом</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Хто є ліричним героєм вірша «Нічна пісня подорожнього»?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Король</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Втомлений подорожній, що звертається до природи й спокою ночі</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дитина</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Птах</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Які образи природи присутні у «Нічній пісні подорожнього» Гете?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Море і кораблі</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вершини гір, тиша лісу, нерухомі верхівки дерев</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Пустеля і піски</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Місто і вулиці</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Який настрій передають ці образи спокою природи у вірші Гете?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Тривогу і неспокій</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Глибокий спокій і бажання відпочинку для втомленої душі</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Радість і веселощі</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Страх перед темрявою</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Що, згідно з останнім рядком вірша Гете, чекає на подорожнього невдовзі?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нова подорож</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Відпочинок і спокій — «зачекай, скоро відпочинеш і ти»</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Буря</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Зустріч з друзями</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що спільного у тому, як Кітс і Гете говорять про природу у своїх віршах?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Обидва описують природу як вороже середовище</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Обидва бачать у природі живий, безперервний голос і джерело спокою чи радості для людини</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Обидва пишуть лише про море</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Обидва уникають згадок про природу</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Чому вірші Кітса і Гете відносять до романтичної лірики?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Через довжину тексту</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Через увагу до почуттів ліричного героя, краси природи й внутрішнього світу людини</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Через історичні події в них</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Через гумористичний тон</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Яку роль відіграє тиша і спокій в обох творах — і в Кітса (зима), і в Гете (ніч)?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони відсутні в обох творах</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>В обох випадках тиша/спокій є особливим, цінним моментом, а не порожнечею</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Тиша означає смерть</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Тиша означає самотність назавжди</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Який художній прийом використовують і Кітс, і Гете, «оживляючи» природу?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Гіпербола</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Персоніфікація — природа «говорить», «співає», «відпочиває», як живі істоти</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Іронія</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Алегорія про тварин</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Чому форма сонета (як у Кітса) вважається складною і вишуканою?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо сонет дуже довгий</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо сонет має чітку, обмежену кількість рядків і риму, яких треба дотримуватися</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо сонет пишеться лише прозою</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо сонет не має рими взагалі</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Чому такі короткі вірші, як «Про коника та цвіркуна» чи «Нічна пісня подорожнього», досі читають через століття?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо вони найдовші у світовій поезії</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо в кількох рядках вони передають почуття, зрозумілі людям у будь-яку епоху</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо їх легко вивчити напам'ять, і тільки тому</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо їх написали відомі автори, а не за зміст</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між поезіями Кітса і Гете?</t>
+          <t>Поезії Кітса і Гете обидві належать до європейського романтизму і оспівують природу.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яке значення мають вірші Кітса і Гете для учнів 5 класу?</t>
+          <t>Вивчення таких коротких ліричних віршів у 5 класі допомагає вчитися помічати красу в простих речах.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Що таке «ліричний герой» у вірші?</t>
+          <t>«Ліричний герой» — це завжди сам автор вірша, без жодної різниці між ними.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Які образи описує Гете у «Нічній пісні подорожнього»?</t>
+          <t>У «Нічній пісні подорожнього» Гете описує вершини гір, тишу лісу і нерухомі верхівки дерев.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Що обіцяє лірику природа у фінальному рядку вірша Гете?</t>
+          <t>Останній рядок вірша Гете обіцяє подорожньому скорий відпочинок.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яке почуття переважає у «Нічній пісні подорожнього»?</t>
+          <t>У «Нічній пісні подорожнього» переважає тривожне, неспокійне почуття.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які художні засоби використовує Кітс у вірші «Про коника та цвіркуна»?</t>
+          <t>Що об'єднує вірші Кітса «Про коника та цвіркуна» і Гете «Нічна пісня подорожнього»?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Метафора (природа ніколи не замовкає)</t>
+          <t>Образи природи як живого голосу</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Протиставлення (літо-зима)</t>
+          <t>Тема спокою і відпочинку</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Числівники</t>
+          <t>Гумористичний сюжет</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Персоніфікація природи</t>
+          <t>Увага до почуттів ліричного героя</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Йоганн Вольфганг Гете — геніальний німецький поет письменник і мислитель</t>
+          <t>Йоганн Вольфганг Гете</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Німеччина — Гете жив у XVIII-XIX ст. і є символом класичної і романтичної традиції</t>
+          <t>Німеччина</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Спокій і тиша ночі — природа замовкає і заспокоює втомленого мандрівника обіцяючи відпочинок</t>
+          <t>Спокій і тиша ночі</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
